--- a/templates/trace_report_template.xlsx
+++ b/templates/trace_report_template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,107 +28,66 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="005A6A85"/>
+      <color rgb="006C757D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <color rgb="00212529"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="006C757D"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00212529"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00212529"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00212529"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <sz val="10"/>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="00212529"/>
+      <sz val="13"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="005A6A85"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="005A6A85"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000F5132"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000F5132"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00842029"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00842029"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001B2A4A"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="005A6A85"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="005A6A85"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000F5132"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000F5132"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="005A6A85"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
+      <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
+      <name val="Meiryo UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
@@ -143,32 +102,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B2A4A"/>
-        <bgColor rgb="001B2A4A"/>
+        <fgColor rgb="00212529"/>
+        <bgColor rgb="00212529"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00F8F9FA"/>
+        <bgColor rgb="00F8F9FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1E7DD"/>
-        <bgColor rgb="00D1E7DD"/>
+        <fgColor rgb="00343A40"/>
+        <bgColor rgb="00343A40"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00E9ECEF"/>
+        <bgColor rgb="00E9ECEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00334E68"/>
-        <bgColor rgb="00334E68"/>
+        <fgColor rgb="00495057"/>
+        <bgColor rgb="00495057"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,37 +141,37 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00DEE2E6"/>
       </left>
       <right style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00DEE2E6"/>
       </right>
       <top style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00DEE2E6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="00DEE2E6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CED4DA"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CED4DA"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CED4DA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00CED4DA"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -223,47 +182,32 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -635,27 +579,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>AWS CloudWatch Transaction Search - Trace Report</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1"/>
-    <row r="4">
+    <row r="3" ht="22" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Log Group:</t>
@@ -677,7 +621,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="20" customHeight="1">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Generated At:</t>
@@ -714,13 +658,13 @@
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>OK (2xx)</t>
         </is>
       </c>
       <c r="I7" s="5" t="n"/>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>ERROR / FAULT</t>
         </is>
@@ -733,34 +677,34 @@
       </c>
       <c r="M7" s="5" t="n"/>
     </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="8" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>{{TOTAL_TRACES}}</t>
         </is>
       </c>
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>{{TOTAL_SPANS}}</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>{{OK_TRACES}}</t>
         </is>
       </c>
       <c r="I8" s="5" t="n"/>
-      <c r="J8" s="10" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>{{ERROR_TRACES}}</t>
         </is>
       </c>
       <c r="K8" s="5" t="n"/>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>{{MAX_DURATION}}</t>
         </is>
@@ -781,60 +725,60 @@
       <c r="L9" s="5" t="n"/>
       <c r="M9" s="5" t="n"/>
     </row>
-    <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+    <row r="11" ht="24" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Trace Summary Table</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="12" t="inlineStr">
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Trace ID</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Start Time</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Root Service</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>Root Operation / URL</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>Duration (ms)</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Spans</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Details Link</t>
         </is>
@@ -868,46 +812,46 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="4" customWidth="1" min="10" max="10"/>
-    <col width="4" customWidth="1" min="11" max="11"/>
-    <col width="4" customWidth="1" min="12" max="12"/>
-    <col width="4" customWidth="1" min="13" max="13"/>
-    <col width="4" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
-    <col width="4" customWidth="1" min="18" max="18"/>
-    <col width="4" customWidth="1" min="19" max="19"/>
-    <col width="4" customWidth="1" min="20" max="20"/>
-    <col width="4" customWidth="1" min="21" max="21"/>
-    <col width="4" customWidth="1" min="22" max="22"/>
-    <col width="4" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
-    <col width="4" customWidth="1" min="27" max="27"/>
-    <col width="4" customWidth="1" min="28" max="28"/>
-    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4.5" customWidth="1" min="10" max="10"/>
+    <col width="4.5" customWidth="1" min="11" max="11"/>
+    <col width="4.5" customWidth="1" min="12" max="12"/>
+    <col width="4.5" customWidth="1" min="13" max="13"/>
+    <col width="4.5" customWidth="1" min="14" max="14"/>
+    <col width="4.5" customWidth="1" min="15" max="15"/>
+    <col width="4.5" customWidth="1" min="16" max="16"/>
+    <col width="4.5" customWidth="1" min="17" max="17"/>
+    <col width="4.5" customWidth="1" min="18" max="18"/>
+    <col width="4.5" customWidth="1" min="19" max="19"/>
+    <col width="4.5" customWidth="1" min="20" max="20"/>
+    <col width="4.5" customWidth="1" min="21" max="21"/>
+    <col width="4.5" customWidth="1" min="22" max="22"/>
+    <col width="4.5" customWidth="1" min="23" max="23"/>
+    <col width="4.5" customWidth="1" min="24" max="24"/>
+    <col width="4.5" customWidth="1" min="25" max="25"/>
+    <col width="4.5" customWidth="1" min="26" max="26"/>
+    <col width="4.5" customWidth="1" min="27" max="27"/>
+    <col width="4.5" customWidth="1" min="28" max="28"/>
+    <col width="4.5" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>AWS X-Ray Trace Timeline &amp; Waterfall View</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1"/>
+    <row r="3" ht="22" customHeight="1"/>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>TRACE ID</t>
         </is>
@@ -915,13 +859,13 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>ROOT SERVICE / OPERATION</t>
         </is>
@@ -930,19 +874,19 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n"/>
-      <c r="M5" s="13" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>TOTAL DURATION</t>
         </is>
       </c>
       <c r="N5" s="5" t="n"/>
-      <c r="O5" s="13" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>TOTAL SPANS</t>
         </is>
       </c>
       <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="13" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>START TIMESTAMP (UTC)</t>
         </is>
@@ -952,8 +896,8 @@
       <c r="T5" s="5" t="n"/>
       <c r="U5" s="5" t="n"/>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="15" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>{{CURRENT_TRACE_ID}}</t>
         </is>
@@ -961,13 +905,13 @@
       <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>{{CURRENT_STATUS}}</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>{{CURRENT_ROOT}}</t>
         </is>
@@ -976,19 +920,19 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
       <c r="L6" s="5" t="n"/>
-      <c r="M6" s="17" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>{{CURRENT_DURATION}}</t>
         </is>
       </c>
       <c r="N6" s="5" t="n"/>
-      <c r="O6" s="17" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>{{CURRENT_SPANS_COUNT}}</t>
         </is>
       </c>
       <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="15" t="inlineStr">
+      <c r="Q6" s="10" t="inlineStr">
         <is>
           <t>{{CURRENT_START_TIME}}</t>
         </is>
@@ -1020,155 +964,155 @@
       <c r="T7" s="5" t="n"/>
       <c r="U7" s="5" t="n"/>
     </row>
-    <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Timeline Segments &amp; Waterfall</t>
         </is>
       </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>Waterfall Timeline (0% ------------------------&gt; 100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Waterfall Timeline (0% ────────────────────────&gt; 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Hierarchy &amp; Operation</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Start Offset</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Duration (ms)</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>% of Trace</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="K10" s="19" t="inlineStr">
+      <c r="K10" s="14" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="L10" s="19" t="inlineStr">
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr">
+      <c r="M10" s="14" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="N10" s="19" t="inlineStr">
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="O10" s="19" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="P10" s="19" t="inlineStr">
+      <c r="P10" s="14" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="Q10" s="19" t="inlineStr">
+      <c r="Q10" s="14" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="R10" s="19" t="inlineStr">
+      <c r="R10" s="14" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="S10" s="19" t="inlineStr">
+      <c r="S10" s="14" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="T10" s="19" t="inlineStr">
+      <c r="T10" s="14" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="U10" s="19" t="inlineStr">
+      <c r="U10" s="14" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="V10" s="19" t="inlineStr">
+      <c r="V10" s="14" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="W10" s="19" t="inlineStr">
+      <c r="W10" s="14" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="X10" s="19" t="inlineStr">
+      <c r="X10" s="14" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="Y10" s="19" t="inlineStr">
+      <c r="Y10" s="14" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="Z10" s="19" t="inlineStr">
+      <c r="Z10" s="14" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="AA10" s="19" t="inlineStr">
+      <c r="AA10" s="14" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="AB10" s="19" t="inlineStr">
+      <c r="AB10" s="14" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="AC10" s="19" t="inlineStr">
+      <c r="AC10" s="14" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -1204,96 +1148,96 @@
   <dimension ref="A2:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>CloudWatch Logs Insights - Exported Spans (aws/spans)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>trace_id</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>span_id</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>parent_span_id</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>service_name</t>
         </is>
       </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>operation_name</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>duration_ms</t>
         </is>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>duration_nano</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>http_status</t>
         </is>
       </c>
-      <c r="J4" s="12" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>http_method</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>http_url</t>
         </is>
       </c>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>status_code</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>status_message</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
